--- a/Result/profitability/2379.xlsx
+++ b/Result/profitability/2379.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>6.70375</v>
+        <v>6.565</v>
       </c>
       <c r="N2" t="n">
-        <v>49.025</v>
+        <v>48.48</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>5.60625</v>
+        <v>5.705</v>
       </c>
       <c r="N3" t="n">
-        <v>47.7375</v>
+        <v>47.56874999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>4.918749999999999</v>
+        <v>4.686249999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>46.8625</v>
+        <v>46.2925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>3.72875</v>
+        <v>3.70375</v>
       </c>
       <c r="N5" t="n">
-        <v>45.09625</v>
+        <v>44.6925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.77</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8725</v>
+        <v>2.96375</v>
       </c>
       <c r="N6" t="n">
-        <v>44.06</v>
+        <v>43.725</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>2.1625</v>
+        <v>2.44375</v>
       </c>
       <c r="N7" t="n">
-        <v>42.89625</v>
+        <v>42.76125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>1.73625</v>
+        <v>1.60875</v>
       </c>
       <c r="N8" t="n">
-        <v>41.94</v>
+        <v>41.6075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>37553</v>
+      </c>
+      <c r="D75" t="n">
+        <v>19902</v>
+      </c>
+      <c r="E75" t="n">
+        <v>17651</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3725</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>645</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4370</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3805</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7.4725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1208530805687204</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.659999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05356423681031008</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.02624671916010501</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.229999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06430420067688625</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
